--- a/data/trans_orig/P80_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P80_R-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>862</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311274</t>
+          <t>317983</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310592</t>
+          <t>314020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288069</t>
+          <t>314973</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280756</t>
+          <t>310688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>599342</t>
+          <t>632957</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591730</t>
+          <t>628624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511409</t>
+          <t>524318</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491811</t>
+          <t>512485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>516879</t>
+          <t>529271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>507414</t>
+          <t>539089</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501057</t>
+          <t>533093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510881</t>
+          <t>542617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1018822</t>
+          <t>1063406</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003122</t>
+          <t>1049616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1025778</t>
+          <t>1069744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513656</t>
+          <t>545175</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513656</t>
+          <t>545175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513656</t>
+          <t>545175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032045</t>
+          <t>1075822</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032045</t>
+          <t>1075822</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032045</t>
+          <t>1075822</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>309108</t>
+          <t>306078</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302924</t>
+          <t>297163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312830</t>
+          <t>310751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>341452</t>
+          <t>348816</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334977</t>
+          <t>342741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345275</t>
+          <t>352944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>650559</t>
+          <t>654895</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642436</t>
+          <t>645267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656333</t>
+          <t>661614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>309040</t>
+          <t>369529</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302097</t>
+          <t>359738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311836</t>
+          <t>372064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>471525</t>
+          <t>417574</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463236</t>
+          <t>410785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474372</t>
+          <t>420530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>780564</t>
+          <t>787104</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>772725</t>
+          <t>778407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785165</t>
+          <t>791858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>205040</t>
+          <t>222995</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200722</t>
+          <t>218243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>383106</t>
+          <t>427925</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378885</t>
+          <t>421758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>266515</t>
+          <t>267751</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>263854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268777</t>
+          <t>269904</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>255941</t>
+          <t>262191</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253447</t>
+          <t>259496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256896</t>
+          <t>263391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>522456</t>
+          <t>529942</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>517867</t>
+          <t>525225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525148</t>
+          <t>532534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38201</t>
+          <t>45941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,67 +2818,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>29625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>45379</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>30895</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>64803</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>3,05%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>36652</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>56487</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>602021</t>
+          <t>691829</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585148</t>
+          <t>672757</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611721</t>
+          <t>703858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,67 +2931,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>831094</t>
+          <t>750441</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>820582</t>
+          <t>739326</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840778</t>
+          <t>757497</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1442270</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1422846</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1456754</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>96,95%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1433114</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1413279</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1447814</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623349</t>
+          <t>718698</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623349</t>
+          <t>718698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623349</t>
+          <t>718698</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>768951</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>768951</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>768951</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469766</t>
+          <t>1487649</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469766</t>
+          <t>1487649</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469766</t>
+          <t>1487649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37587</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,67 +3161,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>42759</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>30868</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>58972</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,63%</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>34905</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>20314</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>49565</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>904358</t>
+          <t>768428</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>890127</t>
+          <t>756253</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>918115</t>
+          <t>778355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,67 +3274,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>704938</t>
+          <t>815725</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>697611</t>
+          <t>806965</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>710501</t>
+          <t>821736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1584154</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1567941</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1596045</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>97,37%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1609296</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1594636</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1623887</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927714</t>
+          <t>796952</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927714</t>
+          <t>796952</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927714</t>
+          <t>796952</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>829960</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>829960</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>829960</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644201</t>
+          <t>1626913</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644201</t>
+          <t>1626913</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644201</t>
+          <t>1626913</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>60769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>104966</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63275</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91253</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>141103</t>
+          <t>164756</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3391790</t>
+          <t>3450847</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3368649</t>
+          <t>3424953</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3412246</t>
+          <t>3469150</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3605471</t>
+          <t>3671806</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3591344</t>
+          <t>3656141</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3618615</t>
+          <t>3683414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6997261</t>
+          <t>7122653</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6970720</t>
+          <t>7092094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7020570</t>
+          <t>7146288</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
